--- a/WorkBot/refactor-experimental/data/orders/Sysco/Sysco_Collegetown_20251114.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Sysco/Sysco_Collegetown_20251114.xlsx
@@ -454,20 +454,14 @@
           <t>Nutella</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>69.49</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>69.49</t>
-        </is>
+      <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>69.48999999999999</v>
+      </c>
+      <c r="E2" t="n">
+        <v>69.48999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -481,20 +475,14 @@
           <t>PKT Mayo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>37.99</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>37.99</t>
-        </is>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>37.99</v>
+      </c>
+      <c r="E3" t="n">
+        <v>37.99</v>
       </c>
     </row>
     <row r="4">
@@ -508,20 +496,14 @@
           <t>Tomato - Fresh Sliced</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>32.18</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>64.36</t>
-        </is>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>32.18</v>
+      </c>
+      <c r="E4" t="n">
+        <v>64.36</v>
       </c>
     </row>
     <row r="5">
@@ -535,20 +517,14 @@
           <t>Avocado - Halves Fresh</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>33.90</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>33.90</t>
-        </is>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="E5" t="n">
+        <v>33.9</v>
       </c>
     </row>
     <row r="6">
@@ -562,20 +538,14 @@
           <t>Mozz (Sliced)</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>28.40</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>56.80</t>
-        </is>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>28.4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>56.8</v>
       </c>
     </row>
     <row r="7">
@@ -589,20 +559,14 @@
           <t>Egg Patty</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>47.08</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>188.32</t>
-        </is>
+      <c r="C7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" t="n">
+        <v>47.08</v>
+      </c>
+      <c r="E7" t="n">
+        <v>188.32</v>
       </c>
     </row>
     <row r="8">
@@ -616,20 +580,14 @@
           <t>Sausage - Patty (1.5oz)</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>25.25</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>50.50</t>
-        </is>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="E8" t="n">
+        <v>50.5</v>
       </c>
     </row>
     <row r="9">
@@ -643,20 +601,14 @@
           <t>Smoothie Ice Cream</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>81.15</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>81.15</t>
-        </is>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>81.15000000000001</v>
+      </c>
+      <c r="E9" t="n">
+        <v>81.15000000000001</v>
       </c>
     </row>
     <row r="10">
@@ -670,20 +622,14 @@
           <t>Hash Brown</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>23.89</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>95.56</t>
-        </is>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>23.89</v>
+      </c>
+      <c r="E10" t="n">
+        <v>95.56</v>
       </c>
     </row>
     <row r="11">
@@ -697,20 +643,14 @@
           <t>Sausage - Vegan Patty</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>91.20</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>182.40</t>
-        </is>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>182.4</v>
       </c>
     </row>
     <row r="12">
@@ -724,20 +664,14 @@
           <t>Cakerie - Cake Chocolate Dreamin' GF</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>80.99</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>80.99</t>
-        </is>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>80.98999999999999</v>
+      </c>
+      <c r="E12" t="n">
+        <v>80.98999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -751,20 +685,14 @@
           <t>Gatorade Cool Blue</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>29.40</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>29.40</t>
-        </is>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E13" t="n">
+        <v>29.4</v>
       </c>
     </row>
     <row r="14">
@@ -778,20 +706,14 @@
           <t>Naked - Green Machine</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>24.24</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>24.24</t>
-        </is>
+      <c r="C14" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>24.24</v>
+      </c>
+      <c r="E14" t="n">
+        <v>24.24</v>
       </c>
     </row>
     <row r="15">
@@ -805,20 +727,14 @@
           <t>Naked - Blue Machine</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>24.24</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>24.24</t>
-        </is>
+      <c r="C15" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>24.24</v>
+      </c>
+      <c r="E15" t="n">
+        <v>24.24</v>
       </c>
     </row>
     <row r="16">
@@ -832,20 +748,14 @@
           <t>Chobani - Peach</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>15.39</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>15.39</t>
-        </is>
+      <c r="C16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>15.39</v>
+      </c>
+      <c r="E16" t="n">
+        <v>15.39</v>
       </c>
     </row>
     <row r="17">
@@ -859,20 +769,14 @@
           <t>Chobani - Black Cherry</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>15.39</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>15.39</t>
-        </is>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>15.39</v>
+      </c>
+      <c r="E17" t="n">
+        <v>15.39</v>
       </c>
     </row>
     <row r="18">
@@ -886,20 +790,14 @@
           <t>SABRA - Hummus Classic With Pretzels</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>32.74</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>32.74</t>
-        </is>
+      <c r="C18" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>32.74</v>
+      </c>
+      <c r="E18" t="n">
+        <v>32.74</v>
       </c>
     </row>
     <row r="19">
@@ -913,20 +811,14 @@
           <t>SABRA - Hummus Roasted Garlic With Pretzels</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>32.20</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>32.20</t>
-        </is>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>32.2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>32.2</v>
       </c>
     </row>
   </sheetData>
